--- a/data/trans_bre/P32C-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P32C-Provincia-trans_bre.xlsx
@@ -660,17 +660,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 2,02</t>
+          <t>-6,66; 1,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,35; -1,96</t>
+          <t>-10,28; -1,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 1,95</t>
+          <t>-6,25; 2,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -685,12 +685,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -8,94</t>
+          <t>-100,0; 28,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 304,94</t>
+          <t>-100,0; 294,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,17 +760,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,33; -0,89</t>
+          <t>-5,32; -0,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,42; -0,56</t>
+          <t>-3,79; -0,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,64; -1,2</t>
+          <t>-6,01; -1,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 0,0</t>
+          <t>-3,0; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -870,12 +870,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 2,46</t>
+          <t>-1,44; 2,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 1,48</t>
+          <t>-3,01; 1,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 331,39</t>
         </is>
       </c>
     </row>
@@ -960,12 +960,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 2,28</t>
+          <t>-4,16; 2,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,85; -0,52</t>
+          <t>-4,9; -0,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -975,12 +975,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 0,82</t>
+          <t>-2,56; 0,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 706,1</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1060,12 +1060,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 14,5</t>
+          <t>-1,83; 14,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,39; -0,71</t>
+          <t>-6,68; -0,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,67</t>
+          <t>0,0; 23,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 2,77</t>
+          <t>-1,97; 3,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 0,0</t>
+          <t>-3,11; 0,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 0,0</t>
+          <t>-3,22; 0,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 4,09</t>
+          <t>-2,11; 4,51</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 834,19</t>
         </is>
       </c>
     </row>
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,91; -0,97</t>
+          <t>-4,96; -1,2</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,4; -0,04</t>
+          <t>-3,47; -0,04</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,96; -0,58</t>
+          <t>-4,21; -0,59</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 1,52</t>
+          <t>-3,89; 1,88</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1285,17 +1285,17 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 105,87</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 47,91</t>
+          <t>-100,0; -1,8</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 118,14</t>
+          <t>-100,0; 134,14</t>
         </is>
       </c>
     </row>
@@ -1360,27 +1360,27 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 1,83</t>
+          <t>-1,65; 1,87</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 0,26</t>
+          <t>-2,9; 0,47</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 1,56</t>
+          <t>-1,38; 1,67</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-2,78; -0,24</t>
+          <t>-2,6; -0,23</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 260,54</t>
+          <t>-100,0; 291,97</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 0,04</t>
+          <t>-1,78; 0,06</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,42; -1,02</t>
+          <t>-2,55; -1,07</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,72; -0,32</t>
+          <t>-1,75; -0,36</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 0,82</t>
+          <t>-1,13; 0,65</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-81,15; 8,69</t>
+          <t>-81,61; 11,63</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-96,28; -53,5</t>
+          <t>-96,19; -54,77</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-86,06; -15,6</t>
+          <t>-88,16; -18,34</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-69,78; 93,38</t>
+          <t>-72,37; 69,4</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P32C-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P32C-Provincia-trans_bre.xlsx
@@ -660,17 +660,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 1,84</t>
+          <t>-7,06; 1,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,28; -1,81</t>
+          <t>-10,65; -2,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 2,03</t>
+          <t>-7,23; 1,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -685,12 +685,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 28,96</t>
+          <t>-100,0; 1,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 294,72</t>
+          <t>-100,0; 154,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,17 +760,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,32; -0,92</t>
+          <t>-5,68; -1,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,79; -0,61</t>
+          <t>-3,4; -0,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,01; -1,21</t>
+          <t>-5,58; -1,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,95</t>
+          <t>-1,27</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-44,85%</t>
+          <t>-51,35%</t>
         </is>
       </c>
     </row>
@@ -860,7 +860,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 0,0</t>
+          <t>-2,64; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -870,12 +870,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 2,43</t>
+          <t>-1,82; 2,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 1,93</t>
+          <t>-3,43; 1,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 331,39</t>
+          <t>-100,0; 169,99</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,57</t>
+          <t>-0,45</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-44,14%</t>
+          <t>-38,89%</t>
         </is>
       </c>
     </row>
@@ -960,12 +960,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 2,07</t>
+          <t>-4,07; 2,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,9; -0,53</t>
+          <t>-5,39; -0,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 0,99</t>
+          <t>-2,36; 1,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,13</t>
+          <t>4,33</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1060,12 +1060,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 14,46</t>
+          <t>-0,97; 13,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,68; -0,71</t>
+          <t>-7,16; -0,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,83</t>
+          <t>0,0; 23,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,46</t>
+          <t>0,49</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>27,71%</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 3,0</t>
+          <t>-1,99; 3,16</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 0,0</t>
+          <t>-2,47; 0,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 0,0</t>
+          <t>-2,73; 0,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 4,51</t>
+          <t>-2,22; 4,38</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 834,19</t>
+          <t>-100,0; 1124,1</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-1,07</t>
+          <t>0,92</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-48,01%</t>
+          <t>46,1%</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,96; -1,2</t>
+          <t>-5,08; -0,97</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,21; -0,59</t>
+          <t>-4,01; -0,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 1,88</t>
+          <t>-1,69; 5,24</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1285,17 +1285,17 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 105,87</t>
+          <t>-100,0; 84,82</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -1,8</t>
+          <t>-100,0; 40,0</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 134,14</t>
+          <t>-78,47; 568,56</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-0,97</t>
+          <t>-0,96</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 1,87</t>
+          <t>-1,57; 2,13</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 0,47</t>
+          <t>-3,01; 0,24</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 1,67</t>
+          <t>-1,38; 1,72</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-2,6; -0,23</t>
+          <t>-2,75; -0,23</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 291,97</t>
+          <t>-100,0; 324,73</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 150,98</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-0,29</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-24,41%</t>
+          <t>8,29%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 0,06</t>
+          <t>-1,81; 0,09</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,55; -1,07</t>
+          <t>-2,52; -1,03</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,75; -0,36</t>
+          <t>-1,79; -0,4</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 0,65</t>
+          <t>-0,76; 1,37</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-81,61; 11,63</t>
+          <t>-78,91; 16,45</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-96,19; -54,77</t>
+          <t>-100,0; -57,08</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-88,16; -18,34</t>
+          <t>-88,23; -26,25</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-72,37; 69,4</t>
+          <t>-56,96; 148,62</t>
         </is>
       </c>
     </row>
